--- a/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
+++ b/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21278DF-DED9-4A41-B500-D1196E82F419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA45AA1-A075-46A8-BFF3-7975D221835A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="AddOpportunity" sheetId="12" r:id="rId5"/>
     <sheet name="AddContact" sheetId="14" r:id="rId6"/>
     <sheet name="Stage" sheetId="16" r:id="rId7"/>
+    <sheet name="ValidationList" sheetId="17" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="84">
   <si>
     <t>James Craven</t>
   </si>
@@ -248,9 +249,6 @@
     <t>Kristian M. Whalen</t>
   </si>
   <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
     <t>Buyside</t>
   </si>
   <si>
@@ -276,6 +274,27 @@
   </si>
   <si>
     <t>Dead</t>
+  </si>
+  <si>
+    <t>Ajay Nair</t>
+  </si>
+  <si>
+    <t>System Admin</t>
+  </si>
+  <si>
+    <t>Validations</t>
+  </si>
+  <si>
+    <t>Tail ExpiresDead/Hold Comments</t>
+  </si>
+  <si>
+    <t>Went To Market?OutcomeTail ExpiresPreparation Effort</t>
+  </si>
+  <si>
+    <t>Debt Capital Markets</t>
+  </si>
+  <si>
+    <t>Verbally Engaged</t>
   </si>
 </sst>
 </file>
@@ -994,13 +1013,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1008,7 +1027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1023,14 +1042,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1038,12 +1057,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1054,17 +1081,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1077,24 +1104,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1106,16 +1133,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1126,7 +1153,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1207,7 +1234,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1215,10 +1242,10 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>40</v>
@@ -1299,7 +1326,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -1307,10 +1334,10 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>40</v>
@@ -1391,7 +1418,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1399,10 +1426,10 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>40</v>
@@ -1493,19 +1520,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
@@ -1531,7 +1558,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -1564,25 +1591,58 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9447574-C5CB-49C4-BC94-993C1D07E71B}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC132F1A-FA50-44C9-8CB7-BC3C8EC453FE}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="67.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
+++ b/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA45AA1-A075-46A8-BFF3-7975D221835A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EB542F-067E-45D7-AEB0-175C3E385282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="83">
   <si>
     <t>James Craven</t>
   </si>
@@ -292,9 +292,6 @@
   </si>
   <si>
     <t>Debt Capital Markets</t>
-  </si>
-  <si>
-    <t>Verbally Engaged</t>
   </si>
 </sst>
 </file>
@@ -1013,13 +1010,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1027,7 +1024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1043,13 +1040,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1057,7 +1054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -1065,7 +1062,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>77</v>
       </c>
@@ -1081,17 +1078,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1104,22 +1101,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1133,16 +1130,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,7 +1231,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1326,7 +1323,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -1418,7 +1415,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1520,19 +1517,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
@@ -1558,7 +1555,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -1591,30 +1588,25 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9447574-C5CB-49C4-BC94-993C1D07E71B}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1625,22 +1617,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC132F1A-FA50-44C9-8CB7-BC3C8EC453FE}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="67.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>

--- a/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
+++ b/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EB542F-067E-45D7-AEB0-175C3E385282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D199CD98-9B50-4E59-AA5B-08B5203996EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25044" yWindow="1248" windowWidth="21600" windowHeight="11160" tabRatio="548" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -291,7 +291,7 @@
     <t>Went To Market?OutcomeTail ExpiresPreparation Effort</t>
   </si>
   <si>
-    <t>Debt Capital Markets</t>
+    <t>Debt Financing</t>
   </si>
 </sst>
 </file>

--- a/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
+++ b/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D199CD98-9B50-4E59-AA5B-08B5203996EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306582F4-0A0A-439D-BAC4-C562D90D3D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25044" yWindow="1248" windowWidth="21600" windowHeight="11160" tabRatio="548" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="84">
   <si>
     <t>James Craven</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Debt Financing</t>
+  </si>
+  <si>
+    <t>Verbally Engaged</t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9447574-C5CB-49C4-BC94-993C1D07E71B}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -1607,6 +1610,11 @@
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
+++ b/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306582F4-0A0A-439D-BAC4-C562D90D3D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B769D7FD-0217-4950-9640-DC61EED6C42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -264,9 +264,6 @@
     <t>Engagements</t>
   </si>
   <si>
-    <t>Jennie Stewart</t>
-  </si>
-  <si>
     <t>Hold</t>
   </si>
   <si>
@@ -295,6 +292,9 @@
   </si>
   <si>
     <t>Verbally Engaged</t>
+  </si>
+  <si>
+    <t>Brian Miller</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
         <v>77</v>
-      </c>
-      <c r="B3" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1426,7 +1426,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
         <v>71</v>
@@ -1599,22 +1599,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1632,17 +1632,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
+++ b/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B769D7FD-0217-4950-9640-DC61EED6C42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855B4684-B045-416E-8BF1-6CE16EE97C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="83">
   <si>
     <t>James Craven</t>
   </si>
@@ -289,9 +289,6 @@
   </si>
   <si>
     <t>Debt Financing</t>
-  </si>
-  <si>
-    <t>Verbally Engaged</t>
   </si>
   <si>
     <t>Brian Miller</t>
@@ -1059,7 +1056,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1591,7 +1588,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9447574-C5CB-49C4-BC94-993C1D07E71B}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -1610,11 +1607,6 @@
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
+++ b/TestData/LV_TMTT0046653_VerifyTailExpireFieldOnCFEngagementwithJobTypeShowsValidationWhileChangingStage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855B4684-B045-416E-8BF1-6CE16EE97C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67231925-F8C2-4147-A334-6BD6531DAFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="86">
   <si>
     <t>James Craven</t>
   </si>
@@ -292,6 +292,15 @@
   </si>
   <si>
     <t>Brian Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permission Set </t>
+  </si>
+  <si>
+    <t>CAO MA, CAO CS</t>
+  </si>
+  <si>
+    <t>Verbally Engaged</t>
   </si>
 </sst>
 </file>
@@ -1039,30 +1048,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -1588,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9447574-C5CB-49C4-BC94-993C1D07E71B}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -1607,6 +1623,11 @@
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
